--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/keeper_garden.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/keeper_garden.xlsx
@@ -428,7 +428,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Caminhe para onde quiser. Todos os caminhos levam à mesma vista.</t>
+          <t>Ande onde quiser. Todo caminho leva à mesma vista.</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Florescimento de Laços.</t>
+          <t>Floração dos Laços.</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Por que os gatos são tão insuportavelmente fofos, eu me pergunto?</t>
+          <t>Por que os gatos são insuportavelmente fofos, me pergunto?</t>
         </is>
       </c>
     </row>
@@ -601,8 +601,8 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Você também acha? Muwohoho... claro que acha.
-Eu gostaria de mergulhar numa fonte termal com gatos prateados e ficar brincando na água por um tempo…</t>
+          <t>Você acha também, né? Muwohoho... claro que acha.
+Queria poder me afundar numa fonte termal com gatas prateadas e me espirrar por um tempo...</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>...Opa, parece que eu deixei cair alguma coisa!</t>
+          <t>...Opa, parece que derrubei algo!</t>
         </is>
       </c>
     </row>
